--- a/data/daily/2026-08/2026-08-26.xlsx
+++ b/data/daily/2026-08/2026-08-26.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,35 +1317,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1425,27 +1425,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,24 +1478,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1503,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,79 +1528,54 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -3089,27 +3089,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -3124,27 +3124,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
           <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
           <t>17,900원</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,27 +4062,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
@@ -4097,34 +4097,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>유한양행 프레쉬츄 생유산균 30정 30일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4147,19 +4147,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651651&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/Mz4AWbpywwVFSrdyow4Z600651651_00_00Mz4AWbpywwVFSrdyow4Z.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,34 +4167,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,34 +4202,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627033&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618639&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260819/2NKz5YxykngJc58J5cja032627033_00_012NKz5YxykngJc58J5cja.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260703/B8ckjHxaPLARUlbtHVdP601618639_00_02B8ckjHxaPLARUlbtHVdP.jpg</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4247,24 +4247,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,34 +4272,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,34 +4307,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>홀베리 유기농 10포 레몬생강즙</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/0AapsR84t6vSDwtqGuP2965923424_00_000AapsR84t6vSDwtqGuP2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,34 +4342,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618634&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/G3OpB4vFrKk7H6gBBjO3601618634_00_00G3OpB4vFrKk7H6gBBjO3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762105&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/6YtHsleJV0YMOtFdtOAk901762105_00_016YtHsleJV0YMOtFdtOAk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
     </row>
@@ -4569,52 +4569,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>동화약품</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>종근당</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 프레쉬츄 생유산균 30정 30일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 10포 레몬생강즙</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
         </is>
       </c>
     </row>
@@ -4683,52 +4683,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5060,24 +5060,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>25,500원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993407ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[8월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259818&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025981802ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
+          <t>[8월올영픽+더블증정] 셀트리온 홀드잇 매드 MAD 10+2정 (+2정 온라인)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>이너랩</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25,500원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254467&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993407ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025446723ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[다이어트 유산균] 것시스 다이어트 B프로 14캡슐 (14일분) / 체지방CUT</t>
+          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>것시스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227154&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259818&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022715431ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025981802ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5355,22 +5355,22 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5412,22 +5412,22 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>이너랩</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>것시스</t>
         </is>
       </c>
     </row>
@@ -5464,27 +5464,27 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[8월올영픽+더블증정] 셀트리온 홀드잇 매드 MAD 10+2정 (+2정 온라인)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[1등 유산균] 콜레올로지 컷 다이어트 유산균 20캡슐 (10일분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[다이어트 유산균] 것시스 다이어트 B프로 14캡슐 (14일분) / 체지방CUT</t>
         </is>
       </c>
     </row>
@@ -5521,27 +5521,27 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
+          <t>25,500원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>55,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
           <t>11,900원</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>22,900원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>25,500원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5680,10 +5680,10 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -5727,13 +5727,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5743,19 +5743,19 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5768,23 +5768,23 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5803,16 +5803,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5821,22 +5821,66 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
       </c>
     </row>
